--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T10:29:33+00:00</t>
+    <t>2026-03-01T15:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T15:46:45+00:00</t>
+    <t>2026-03-02T16:20:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T16:20:44+00:00</t>
+    <t>2026-03-02T17:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T17:40:54+00:00</t>
+    <t>2026-03-03T16:09:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T16:09:57+00:00</t>
+    <t>2026-03-03T18:16:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T18:16:34+00:00</t>
+    <t>2026-03-03T20:10:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
